--- a/XLibur.Tests/Resource/Other/Drawings/GroupedPictures.xlsx
+++ b/XLibur.Tests/Resource/Other/Drawings/GroupedPictures.xlsx
@@ -61,7 +61,7 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="1000000" y="1000000"/>
-          <a:ext cx="5000000" cy="4000000"/>
+          <a:ext cx="10000000" cy="8000000"/>
           <a:chOff x="1000000" y="1000000"/>
           <a:chExt cx="5000000" cy="4000000"/>
         </a:xfrm>
@@ -105,7 +105,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="3500000" y="2500000"/>
-            <a:ext cx="2000000" cy="2000000"/>
+            <a:ext cx="1500000" cy="1500000"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
